--- a/executa_obma/Resultados Planilha/comparacao_irace_vs_padrao.xlsx
+++ b/executa_obma/Resultados Planilha/comparacao_irace_vs_padrao.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Desktop\irace\resultados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Desktop\irace\resultados\Resultados Planilha\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1E6D30-43C3-4632-938F-4024AB117883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B7157D-FF4B-433C-9CD6-D3B0200EC5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12504" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Instância</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>MDG-a_40</t>
+  </si>
+  <si>
+    <t>great cost</t>
   </si>
 </sst>
 </file>
@@ -96,7 +99,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -119,13 +122,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -432,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -442,7 +459,7 @@
     <col min="5" max="5" width="36.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -458,8 +475,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -475,8 +495,11 @@
       <c r="E2">
         <v>8.2154340000000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>114327</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -492,8 +515,11 @@
       <c r="E3">
         <v>8.3361180000000008</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>114093</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -509,8 +535,11 @@
       <c r="E4">
         <v>8.318327</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4">
+        <v>114265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -526,8 +555,11 @@
       <c r="E5">
         <v>8.6163720000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5">
+        <v>114327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -543,8 +575,11 @@
       <c r="E6">
         <v>8.508699</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>114229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -560,8 +595,11 @@
       <c r="E7">
         <v>8.4193599999999993</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>114214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -577,8 +615,11 @@
       <c r="E8">
         <v>7.8391659999999996</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8">
+        <v>114216</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -594,8 +635,11 @@
       <c r="E9">
         <v>8.3880359999999996</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9">
+        <v>114335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -611,8 +655,11 @@
       <c r="E10">
         <v>7.6724949999999996</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <v>114408</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -627,6 +674,9 @@
       </c>
       <c r="E11">
         <v>8.5553500000000007</v>
+      </c>
+      <c r="F11">
+        <v>114349</v>
       </c>
     </row>
   </sheetData>
